--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_226_R23.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_226_R23.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.762</v>
+        <v>5.7744</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0607</v>
+        <v>2.8379</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7013</v>
+        <v>2.9365</v>
       </c>
       <c r="G2" t="n">
         <v>4.7847</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3536</v>
+        <v>-0.6339</v>
       </c>
       <c r="T2" t="n">
-        <v>1.172</v>
+        <v>-0.0507</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8184</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8623</v>
+        <v>4.2818</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0304</v>
+        <v>2.6516</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8319</v>
+        <v>1.6303</v>
       </c>
       <c r="G3" t="n">
         <v>5.335</v>
@@ -688,13 +688,13 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9366</v>
+        <v>-0.5171</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0455</v>
+        <v>-0.4244</v>
       </c>
       <c r="U3" t="n">
-        <v>0.109</v>
+        <v>-0.0927</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5361</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9895</v>
+        <v>1.0642</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.7653</v>
+        <v>-1.6906</v>
       </c>
       <c r="F4" t="n">
         <v>2.7548</v>
@@ -766,10 +766,10 @@
         <v>3.9432</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9946</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4674</v>
+        <v>-0.3927</v>
       </c>
       <c r="U4" t="n">
         <v>-0.5272</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2452</v>
+        <v>0.1947</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5909</v>
+        <v>-0.0958</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8361</v>
+        <v>0.2905</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4149</v>
+        <v>0.0001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3447</v>
+        <v>0.0168</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0702</v>
+        <v>-0.0167</v>
       </c>
       <c r="J5" t="n">
-        <v>1.204</v>
+        <v>0.0536</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6554</v>
+        <v>0.0168</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5486</v>
+        <v>0.0368</v>
       </c>
       <c r="M5" t="n">
-        <v>0.211</v>
+        <v>-0.0535</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6893</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4783</v>
+        <v>-0.0535</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0154</v>
+        <v>0.232</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7934</v>
+        <v>-0.0373</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4753</v>
+        <v>-0.1494</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.318</v>
+        <v>0.112</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1275</v>
+        <v>0.0989</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0958</v>
+        <v>-1.6027</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2232</v>
+        <v>1.7017</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0001</v>
+        <v>1.4149</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0168</v>
+        <v>1.3447</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0167</v>
+        <v>0.0702</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0536</v>
+        <v>1.204</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0168</v>
+        <v>0.6554</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0368</v>
+        <v>0.5486</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0535</v>
+        <v>0.211</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.6893</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0535</v>
+        <v>-0.4783</v>
       </c>
       <c r="P6" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>0.232</v>
+        <v>3.0154</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1046</v>
+        <v>-0.9397</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1494</v>
+        <v>-0.4872</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0448</v>
+        <v>-0.4525</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VOIGTMANN</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7027</v>
+        <v>-0.4117</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4031</v>
+        <v>-1.2112</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7004</v>
+        <v>0.7996</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4359</v>
+        <v>-1.3621</v>
       </c>
       <c r="H7" t="n">
-        <v>0.371</v>
+        <v>-0.6795</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8068</v>
+        <v>-0.6826</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5069</v>
+        <v>-1.4551</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4033</v>
+        <v>-0.6687</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9102</v>
+        <v>-0.7863</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.929</v>
+        <v>0.093</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0323</v>
+        <v>-0.0108</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8966</v>
+        <v>0.1038</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7332</v>
+        <v>0.2546</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2636</v>
+        <v>0.2438</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4696</v>
+        <v>0.0108</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>N. DIMITRIJEVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7484</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4471</v>
+        <v>-1.3334</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6988</v>
+        <v>0.4942</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3621</v>
+        <v>1.0408</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6795</v>
+        <v>1.0742</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6826</v>
+        <v>-0.0334</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4551</v>
+        <v>1.5411</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6687</v>
+        <v>1.1497</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7863</v>
+        <v>0.3914</v>
       </c>
       <c r="M8" t="n">
-        <v>0.093</v>
+        <v>-0.5003</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0108</v>
+        <v>-0.0755</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1038</v>
+        <v>-0.4248</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.3233</v>
       </c>
       <c r="T8" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.3025</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0901</v>
+        <v>-0.0209</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.3247</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.2525</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. DIMITRIJEVIC</t>
+          <t>D. MCCORMACK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2341</v>
+        <v>-0.9102</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7619</v>
+        <v>-0.4742</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5278</v>
+        <v>-0.4361</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0408</v>
+        <v>-1.9064</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0742</v>
+        <v>0.2651</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0334</v>
+        <v>-2.1715</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5411</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1497</v>
+        <v>-0.1744</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3914</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5003</v>
+        <v>-0.9825</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0755</v>
+        <v>0.4395</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4248</v>
+        <v>-1.422</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7183</v>
+        <v>-0.0914</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.731</v>
+        <v>-0.0863</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0127</v>
+        <v>-0.005</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3247</v>
+        <v>-0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.2525</v>
+        <v>0.5361</v>
       </c>
       <c r="X9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MCCORMACK</t>
+          <t>J. VOIGTMANN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6487</v>
+        <v>-0.9887</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9774</v>
+        <v>-1.521</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6713</v>
+        <v>0.5324</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9064</v>
+        <v>-1.4359</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2651</v>
+        <v>0.371</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1715</v>
+        <v>-1.8068</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-0.5069</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1744</v>
+        <v>0.4033</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.9102</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9825</v>
+        <v>-0.929</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4395</v>
+        <v>-0.0323</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.422</v>
+        <v>-0.8966</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8298</v>
+        <v>0.4472</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5895</v>
+        <v>0.1456</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2403</v>
+        <v>0.3016</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.3808</v>
+        <v>-5.7761</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.2442</v>
+        <v>-6.5051</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8635</v>
+        <v>0.729</v>
       </c>
       <c r="G11" t="n">
         <v>-7.2961</v>
@@ -1312,13 +1312,13 @@
         <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4042</v>
+        <v>0.2005</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1949</v>
+        <v>-0.4558</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7907</v>
+        <v>0.6563</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.9883</v>
+        <v>-7.0845</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.1713</v>
+        <v>-8.3011</v>
       </c>
       <c r="F12" t="n">
-        <v>1.183</v>
+        <v>1.2166</v>
       </c>
       <c r="G12" t="n">
         <v>-3.9335</v>
@@ -1390,13 +1390,13 @@
         <v>2.3195</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8228</v>
+        <v>-0.919</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1687</v>
+        <v>-0.2985</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6541</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0722</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.716499999999998</v>
+        <v>-4.596399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-18.3659</v>
+        <v>-17.2456</v>
       </c>
       <c r="F13" t="n">
         <v>12.6495</v>
@@ -1435,7 +1435,7 @@
         <v>-2.9981</v>
       </c>
       <c r="H13" t="n">
-        <v>6.722000000000002</v>
+        <v>6.722</v>
       </c>
       <c r="I13" t="n">
         <v>-9.719999999999999</v>
@@ -1447,7 +1447,7 @@
         <v>2.650699999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.845000000000001</v>
+        <v>-2.845</v>
       </c>
       <c r="M13" t="n">
         <v>-2.8036</v>
@@ -1456,7 +1456,7 @@
         <v>4.0712</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.8747</v>
+        <v>-6.874700000000001</v>
       </c>
       <c r="P13" t="n">
         <v>6.958700000000001</v>
@@ -1468,10 +1468,10 @@
         <v>22.0356</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.599600000000001</v>
+        <v>-3.4793</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.3782</v>
+        <v>-2.2581</v>
       </c>
       <c r="U13" t="n">
         <v>-1.2213</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0281</v>
+        <v>6.0572</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9115</v>
+        <v>2.0859</v>
       </c>
       <c r="F14" t="n">
-        <v>4.1166</v>
+        <v>3.9714</v>
       </c>
       <c r="G14" t="n">
         <v>3.1372</v>
@@ -1546,13 +1546,13 @@
         <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>3.195</v>
+        <v>2.2242</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6948</v>
+        <v>0.8691</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5002</v>
+        <v>1.355</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1945</v>
+        <v>4.334</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0608</v>
+        <v>-0.471</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2552</v>
+        <v>4.805</v>
       </c>
       <c r="G15" t="n">
         <v>5.9808</v>
@@ -1624,13 +1624,13 @@
         <v>3.0154</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1568</v>
+        <v>1.2964</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2434</v>
+        <v>0.3464</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4002</v>
+        <v>0.95</v>
       </c>
       <c r="V15" t="n">
         <v>0.5361</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>N. CALATHES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6502</v>
+        <v>2.2268</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.8868</v>
+        <v>0.5886</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5369</v>
+        <v>1.6382</v>
       </c>
       <c r="G16" t="n">
-        <v>1.241</v>
+        <v>2.3139</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3383</v>
+        <v>0.2762</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5793</v>
+        <v>2.0377</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5159</v>
+        <v>2.4465</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1379</v>
+        <v>0.8773</v>
       </c>
       <c r="L16" t="n">
-        <v>0.378</v>
+        <v>1.5692</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7251</v>
+        <v>-0.1326</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4762</v>
+        <v>-0.6012</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2014</v>
+        <v>0.4685</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.3917</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.9432</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5515</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2647</v>
+        <v>0.3047</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4683</v>
+        <v>-0.0745</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7965</v>
+        <v>0.3791</v>
       </c>
       <c r="V16" t="n">
         <v>0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. CALATHES</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.547</v>
+        <v>1.8804</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0011</v>
+        <v>-2.0047</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5481</v>
+        <v>3.8851</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3139</v>
+        <v>1.241</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2762</v>
+        <v>-0.3383</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0377</v>
+        <v>1.5793</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4465</v>
+        <v>0.5159</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8773</v>
+        <v>0.1379</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5692</v>
+        <v>0.378</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1326</v>
+        <v>0.7251</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6012</v>
+        <v>-0.4762</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4685</v>
+        <v>1.2014</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9278</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>-3.9432</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3917</v>
+        <v>2.5515</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3752</v>
+        <v>1.4949</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6642</v>
+        <v>0.3503</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2891</v>
+        <v>1.1446</v>
       </c>
       <c r="V17" t="n">
         <v>0.5361</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.367</v>
+        <v>1.4729</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3331</v>
+        <v>0.9792</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0339</v>
+        <v>0.4936</v>
       </c>
       <c r="G18" t="n">
         <v>-1.0233</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4705</v>
+        <v>-0.3646</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1968</v>
+        <v>-0.1571</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6673</v>
+        <v>-0.2076</v>
       </c>
       <c r="V18" t="n">
         <v>2.3969</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2871</v>
+        <v>-0.1634</v>
       </c>
       <c r="E19" t="n">
         <v>0.7922</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0792</v>
+        <v>-0.9556</v>
       </c>
       <c r="G19" t="n">
         <v>0.3723</v>
@@ -1936,13 +1936,13 @@
         <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6594</v>
+        <v>-0.5357</v>
       </c>
       <c r="T19" t="n">
         <v>-0.224</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4353</v>
+        <v>-0.3117</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.45</v>
+        <v>-1.6516</v>
       </c>
       <c r="E20" t="n">
         <v>-1.1151</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3349</v>
+        <v>-0.5365</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5238</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0738</v>
+        <v>-0.1278</v>
       </c>
       <c r="T20" t="n">
         <v>-0.224</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2978</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9632</v>
+        <v>-2.4572</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.9789</v>
+        <v>-6.6866</v>
       </c>
       <c r="F21" t="n">
-        <v>4.0158</v>
+        <v>4.2295</v>
       </c>
       <c r="G21" t="n">
         <v>-3.6848</v>
@@ -2092,13 +2092,13 @@
         <v>2.3195</v>
       </c>
       <c r="S21" t="n">
-        <v>2.1855</v>
+        <v>1.6915</v>
       </c>
       <c r="T21" t="n">
-        <v>1.4787</v>
+        <v>0.771</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7068</v>
+        <v>0.9206</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3701</v>
+        <v>-4.41</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.6436</v>
+        <v>-6.8179</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2735</v>
+        <v>2.4079</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8153</v>
@@ -2170,13 +2170,13 @@
         <v>2.3195</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7714</v>
+        <v>0.1887</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2617</v>
+        <v>-0.436</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4903</v>
+        <v>0.6247</v>
       </c>
       <c r="V22" t="n">
         <v>1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.716399999999999</v>
+        <v>7.289100000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-12.6495</v>
+        <v>-12.6494</v>
       </c>
       <c r="F23" t="n">
-        <v>18.3659</v>
+        <v>19.9386</v>
       </c>
       <c r="G23" t="n">
         <v>2.998</v>
@@ -2248,13 +2248,13 @@
         <v>15.077</v>
       </c>
       <c r="S23" t="n">
-        <v>4.5993</v>
+        <v>6.1723</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2213</v>
+        <v>1.2212</v>
       </c>
       <c r="U23" t="n">
-        <v>3.3783</v>
+        <v>4.950899999999999</v>
       </c>
       <c r="V23" t="n">
         <v>5.077400000000001</v>
